--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5878-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5878-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FC0D5E59-41F2-48AC-BB60-8319CAB02A2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8F1729A-4A26-491E-901F-9C837B9D7E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{8D8645E1-8885-4450-8DC3-BD61FD3C5CF2}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{D70FA158-3FFC-4126-99C3-470901AE194F}"/>
   </bookViews>
   <sheets>
     <sheet name="5878-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1481,27 +1481,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6F88BFD-02D1-40B5-9935-809812C88F05}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF7B0CA3-A5D9-430C-8E69-21CA768007E3}">
   <dimension ref="A1:X19"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="4" width="6.625" customWidth="1"/>
-    <col min="5" max="5" width="6.25" customWidth="1"/>
-    <col min="6" max="6" width="6.625" customWidth="1"/>
-    <col min="7" max="9" width="6.25" customWidth="1"/>
-    <col min="10" max="10" width="6.625" customWidth="1"/>
-    <col min="11" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="14" width="6.625" customWidth="1"/>
-    <col min="15" max="20" width="6.25" customWidth="1"/>
-    <col min="21" max="21" width="6.625" customWidth="1"/>
-    <col min="22" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.375" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1535,7 +1534,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1571,7 +1570,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1623,7 +1622,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1691,7 +1690,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2024</v>
       </c>
@@ -1763,7 +1762,7 @@
         <v>5.68</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="37">
         <v>2023</v>
       </c>
@@ -1835,7 +1834,7 @@
         <v>5.45</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="35">
         <v>2022</v>
       </c>
@@ -1907,7 +1906,7 @@
         <v>5.74</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>2021</v>
       </c>
@@ -1979,7 +1978,7 @@
         <v>6.48</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="35">
         <v>2020</v>
       </c>
@@ -2051,7 +2050,7 @@
         <v>7.06</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2019</v>
       </c>
@@ -2123,7 +2122,7 @@
         <v>6.98</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="35">
         <v>2018</v>
       </c>
@@ -2195,7 +2194,7 @@
         <v>6.4</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2017</v>
       </c>
@@ -2267,7 +2266,7 @@
         <v>7.29</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="35">
         <v>2016</v>
       </c>
@@ -2339,7 +2338,7 @@
         <v>7.62</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>2015</v>
       </c>
@@ -2411,7 +2410,7 @@
         <v>7.66</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="39">
         <v>2014</v>
       </c>
@@ -2483,7 +2482,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="41"/>
       <c r="B16" s="42"/>
       <c r="C16" s="18" t="s">
@@ -2511,7 +2510,7 @@
       <c r="W16" s="48"/>
       <c r="X16" s="44"/>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>2013</v>
       </c>
@@ -2583,7 +2582,7 @@
         <v>8.57</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2012</v>
       </c>
@@ -2655,7 +2654,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37" t="s">
         <v>41</v>
       </c>
